--- a/Libya_calibration_emissions.xlsx
+++ b/Libya_calibration_emissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexa/Projects/ssp_libya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FA4992-318C-584B-B981-E3063034BACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACE38E0-769E-C948-9C49-2CB88A5A8092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30320" yWindow="-7360" windowWidth="28040" windowHeight="17180" xr2:uid="{F354531C-B6C8-2E43-95F0-0E0BC8B85B97}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
   <si>
     <t>Sector </t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>1.13 </t>
+  </si>
+  <si>
+    <t>Aiustar BAU</t>
   </si>
 </sst>
 </file>
@@ -641,7 +644,7 @@
     <col min="5" max="5" width="48.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -656,7 +659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -672,8 +675,11 @@
       <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -682,7 +688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -697,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -712,10 +718,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -730,7 +736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -739,7 +745,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -748,7 +754,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -757,7 +763,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -772,7 +778,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -781,7 +787,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -790,7 +796,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -799,14 +805,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -932,7 +938,7 @@
         <v>47</v>
       </c>
       <c r="C26" s="1">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
@@ -949,7 +955,7 @@
         <v>51</v>
       </c>
       <c r="C27" s="8">
-        <v>0.57999999999999996</v>
+        <v>0.53</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>52</v>
